--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE1F9A4-23D7-4CA4-BA5B-6C6DC0E2EF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D386D79-360A-479B-82F8-A07867A78931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -537,13 +537,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,92 +560,97 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="C2" s="4">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="D2" s="11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2" s="5">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.78</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C3" s="4">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="D3" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.11</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="C4" s="4">
         <v>419</v>
       </c>
       <c r="D4" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="C5" s="4">
-        <v>497</v>
+        <v>554</v>
       </c>
       <c r="D5" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.89</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="C6" s="4">
-        <v>475</v>
+        <v>536</v>
       </c>
       <c r="D6" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="5">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -656,247 +661,260 @@
         <v>506</v>
       </c>
       <c r="D7" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" s="5">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.44</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C8" s="4">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="D8" s="11">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E8" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="C9" s="4">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="D9" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.78</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C10" s="4">
         <v>543</v>
       </c>
       <c r="D10" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.56</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C11" s="4">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="D11" s="11">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E11" s="5">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.56</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C12" s="4">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="D12" s="11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E12" s="5">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.89</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="D13" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="5">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.33</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C14" s="4">
-        <v>365</v>
+        <v>415</v>
       </c>
       <c r="D14" s="11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5">
-        <v>1.1399999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.22</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C15" s="4">
-        <v>469</v>
+        <v>514</v>
       </c>
       <c r="D15" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E15" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.67</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4">
-        <v>359</v>
+        <v>405</v>
       </c>
       <c r="D16" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C17" s="4">
-        <v>454</v>
+        <v>506</v>
       </c>
       <c r="D17" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="C18" s="4">
-        <v>602</v>
+        <v>645</v>
       </c>
       <c r="D18" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" s="5">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.67</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="7">
-        <v>2231</v>
+        <v>2729</v>
       </c>
       <c r="C19" s="7">
-        <v>7576</v>
+        <v>8284</v>
       </c>
       <c r="D19" s="12">
-        <v>225</v>
+        <v>298</v>
       </c>
       <c r="E19" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.95</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
@@ -1076,9 +1094,15 @@
       <c r="J2" s="4">
         <v>108</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="K2" s="4">
+        <v>73</v>
+      </c>
+      <c r="L2" s="4">
+        <v>35</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -1098,7 +1122,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="11">
-        <v>646</v>
+        <v>754</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1132,9 +1156,15 @@
       <c r="J3" s="4">
         <v>104</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="K3" s="4">
+        <v>71</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -1154,7 +1184,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="11">
-        <v>531</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1188,9 +1218,15 @@
       <c r="J4" s="4">
         <v>106</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>29</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -1210,7 +1246,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="11">
-        <v>549</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1244,9 +1280,15 @@
       <c r="J5" s="4">
         <v>105</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="K5" s="4">
+        <v>91</v>
+      </c>
+      <c r="L5" s="4">
+        <v>27</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -1266,7 +1308,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="11">
-        <v>647</v>
+        <v>765</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1300,9 +1342,15 @@
       <c r="J6" s="4">
         <v>94</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="K6" s="4">
+        <v>92</v>
+      </c>
+      <c r="L6" s="4">
+        <v>8</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -1322,7 +1370,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="11">
-        <v>645</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1356,9 +1404,15 @@
       <c r="J7" s="4">
         <v>107</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
@@ -1412,9 +1466,15 @@
       <c r="J8" s="4">
         <v>114</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="K8" s="4">
+        <v>73</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
@@ -1434,7 +1494,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="11">
-        <v>444</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1468,9 +1528,15 @@
       <c r="J9" s="4">
         <v>88</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="K9" s="4">
+        <v>89</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -1490,7 +1556,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="11">
-        <v>515</v>
+        <v>604</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1524,9 +1590,15 @@
       <c r="J10" s="4">
         <v>111</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <v>18</v>
+      </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1546,7 +1618,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="11">
-        <v>735</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1580,9 +1652,15 @@
       <c r="J11" s="4">
         <v>98</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="K11" s="4">
+        <v>28</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
@@ -1602,7 +1680,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="11">
-        <v>498</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1636,9 +1714,15 @@
       <c r="J12" s="4">
         <v>110</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="K12" s="4">
+        <v>97</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
@@ -1658,7 +1742,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="11">
-        <v>554</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1692,9 +1776,15 @@
       <c r="J13" s="4">
         <v>76</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="K13" s="4">
+        <v>61</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
@@ -1714,7 +1804,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="11">
-        <v>571</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1748,9 +1838,15 @@
       <c r="J14" s="4">
         <v>97</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="K14" s="4">
+        <v>67</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
@@ -1770,7 +1866,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="11">
-        <v>448</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1804,9 +1900,15 @@
       <c r="J15" s="4">
         <v>13</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="K15" s="4">
+        <v>66</v>
+      </c>
+      <c r="L15" s="4">
+        <v>10</v>
+      </c>
+      <c r="M15" s="4">
+        <v>40</v>
+      </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
@@ -1826,7 +1928,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="11">
-        <v>656</v>
+        <v>772</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -1860,9 +1962,15 @@
       <c r="J16" s="4">
         <v>110</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+      <c r="K16" s="4">
+        <v>68</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
@@ -1882,7 +1990,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="11">
-        <v>431</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -1916,9 +2024,15 @@
       <c r="J17" s="4">
         <v>107</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="K17" s="4">
+        <v>67</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -1938,7 +2052,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="11">
-        <v>530</v>
+        <v>597</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -1972,9 +2086,15 @@
       <c r="J18" s="4">
         <v>105</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+      <c r="K18" s="4">
+        <v>66</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
+        <v>30</v>
+      </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -1994,7 +2114,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="11">
-        <v>757</v>
+        <v>853</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2028,9 +2148,15 @@
       <c r="J19" s="7">
         <v>1653</v>
       </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
+      <c r="K19" s="7">
+        <v>1009</v>
+      </c>
+      <c r="L19" s="7">
+        <v>109</v>
+      </c>
+      <c r="M19" s="7">
+        <v>88</v>
+      </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
@@ -2050,7 +2176,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="12">
-        <v>9807</v>
+        <v>11013</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2120,7 +2246,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D386D79-360A-479B-82F8-A07867A78931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFCFC00-2456-45AC-8738-5BCBDAA102B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -223,6 +223,7 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -565,17 +566,18 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="C2" s="4">
-        <v>547</v>
+        <v>697</v>
       </c>
       <c r="D2" s="11">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E2" s="5">
-        <v>2.78</v>
-      </c>
+        <v>3.78</v>
+      </c>
+      <c r="F2" s="15"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -583,17 +585,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="C3" s="4">
-        <v>431</v>
+        <v>588</v>
       </c>
       <c r="D3" s="11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E3" s="5">
-        <v>2.11</v>
-      </c>
+        <v>2.89</v>
+      </c>
+      <c r="F3" s="15"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -601,17 +604,18 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C4" s="4">
-        <v>419</v>
+        <v>498</v>
       </c>
       <c r="D4" s="11">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E4" s="5">
-        <v>2</v>
-      </c>
+        <v>2.78</v>
+      </c>
+      <c r="F4" s="15"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -619,17 +623,18 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C5" s="4">
-        <v>554</v>
+        <v>655</v>
       </c>
       <c r="D5" s="11">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="5">
-        <v>2.89</v>
-      </c>
+        <v>3.33</v>
+      </c>
+      <c r="F5" s="15"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -637,17 +642,18 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="C6" s="4">
-        <v>536</v>
+        <v>699</v>
       </c>
       <c r="D6" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5">
-        <v>2</v>
-      </c>
+        <v>2.89</v>
+      </c>
+      <c r="F6" s="15"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -655,17 +661,18 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="C7" s="4">
-        <v>506</v>
+        <v>667</v>
       </c>
       <c r="D7" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5">
-        <v>1.44</v>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="F7" s="15"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -673,17 +680,18 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C8" s="4">
-        <v>372</v>
+        <v>516</v>
       </c>
       <c r="D8" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5">
-        <v>2.2200000000000002</v>
-      </c>
+        <v>2.89</v>
+      </c>
+      <c r="F8" s="15"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -691,17 +699,18 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="C9" s="4">
-        <v>445</v>
+        <v>598</v>
       </c>
       <c r="D9" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5">
-        <v>2.78</v>
-      </c>
+        <v>3.56</v>
+      </c>
+      <c r="F9" s="15"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -709,17 +718,18 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C10" s="4">
-        <v>543</v>
+        <v>706</v>
       </c>
       <c r="D10" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E10" s="5">
-        <v>1.56</v>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="F10" s="15"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -727,17 +737,18 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C11" s="4">
-        <v>428</v>
+        <v>607</v>
       </c>
       <c r="D11" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="5">
-        <v>2.56</v>
-      </c>
+        <v>2.67</v>
+      </c>
+      <c r="F11" s="15"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -745,17 +756,18 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C12" s="4">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="D12" s="11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E12" s="5">
-        <v>1.89</v>
-      </c>
+        <v>2.33</v>
+      </c>
+      <c r="F12" s="15"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -763,17 +775,18 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4">
-        <v>539</v>
+        <v>633</v>
       </c>
       <c r="D13" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E13" s="5">
-        <v>1.33</v>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="F13" s="15"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -781,17 +794,18 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C14" s="4">
-        <v>415</v>
+        <v>494</v>
       </c>
       <c r="D14" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="5">
-        <v>1.22</v>
-      </c>
+        <v>1.33</v>
+      </c>
+      <c r="F14" s="15"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,17 +813,18 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="C15" s="4">
-        <v>514</v>
+        <v>581</v>
       </c>
       <c r="D15" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E15" s="5">
-        <v>2.67</v>
-      </c>
+        <v>3.22</v>
+      </c>
+      <c r="F15" s="15"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -817,17 +832,18 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C16" s="4">
-        <v>405</v>
+        <v>558</v>
       </c>
       <c r="D16" s="11">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E16" s="5">
-        <v>1</v>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="F16" s="15"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -835,17 +851,18 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4">
-        <v>506</v>
+        <v>688</v>
       </c>
       <c r="D17" s="11">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5">
-        <v>1</v>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="F17" s="15"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -853,17 +870,18 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C18" s="4">
-        <v>645</v>
+        <v>730</v>
       </c>
       <c r="D18" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" s="5">
-        <v>1.67</v>
-      </c>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F18" s="15"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -871,17 +889,18 @@
         <v>23</v>
       </c>
       <c r="B19" s="7">
-        <v>2729</v>
+        <v>3417</v>
       </c>
       <c r="C19" s="7">
-        <v>8284</v>
+        <v>10472</v>
       </c>
       <c r="D19" s="12">
-        <v>298</v>
+        <v>383</v>
       </c>
       <c r="E19" s="8">
-        <v>1.95</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="15"/>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1103,8 +1122,12 @@
       <c r="M2" s="4">
         <v>0</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="N2" s="4">
+        <v>102</v>
+      </c>
+      <c r="O2" s="4">
+        <v>108</v>
+      </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -1122,7 +1145,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="11">
-        <v>754</v>
+        <v>964</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1165,8 +1188,12 @@
       <c r="M3" s="4">
         <v>0</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="N3" s="4">
+        <v>104</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -1184,7 +1211,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="11">
-        <v>602</v>
+        <v>806</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1227,8 +1254,12 @@
       <c r="M4" s="4">
         <v>0</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>106</v>
+      </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -1246,7 +1277,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="11">
-        <v>578</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1289,8 +1320,12 @@
       <c r="M5" s="4">
         <v>0</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>126</v>
+      </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
@@ -1308,7 +1343,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="11">
-        <v>765</v>
+        <v>891</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1351,8 +1386,12 @@
       <c r="M6" s="4">
         <v>0</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="N6" s="4">
+        <v>111</v>
+      </c>
+      <c r="O6" s="4">
+        <v>111</v>
+      </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
@@ -1370,7 +1409,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="11">
-        <v>745</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1413,8 +1452,12 @@
       <c r="M7" s="4">
         <v>0</v>
       </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="N7" s="4">
+        <v>108</v>
+      </c>
+      <c r="O7" s="4">
+        <v>105</v>
+      </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
@@ -1432,7 +1475,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="11">
-        <v>650</v>
+        <v>863</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1475,8 +1518,12 @@
       <c r="M8" s="4">
         <v>0</v>
       </c>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="N8" s="4">
+        <v>109</v>
+      </c>
+      <c r="O8" s="4">
+        <v>110</v>
+      </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -1494,7 +1541,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="11">
-        <v>517</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1537,8 +1584,12 @@
       <c r="M9" s="4">
         <v>0</v>
       </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="N9" s="4">
+        <v>106</v>
+      </c>
+      <c r="O9" s="4">
+        <v>114</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -1556,7 +1607,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="11">
-        <v>604</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1599,8 +1650,12 @@
       <c r="M10" s="4">
         <v>18</v>
       </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="N10" s="4">
+        <v>104</v>
+      </c>
+      <c r="O10" s="4">
+        <v>108</v>
+      </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -1618,7 +1673,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="11">
-        <v>753</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1661,8 +1716,12 @@
       <c r="M11" s="4">
         <v>0</v>
       </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="N11" s="4">
+        <v>101</v>
+      </c>
+      <c r="O11" s="4">
+        <v>105</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -1680,7 +1739,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="11">
-        <v>526</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1723,8 +1782,12 @@
       <c r="M12" s="4">
         <v>0</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="N12" s="4">
+        <v>102</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -1742,7 +1805,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="11">
-        <v>651</v>
+        <v>753</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1785,8 +1848,12 @@
       <c r="M13" s="4">
         <v>0</v>
       </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="N13" s="4">
+        <v>105</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -1804,7 +1871,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="11">
-        <v>632</v>
+        <v>737</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1847,8 +1914,12 @@
       <c r="M14" s="4">
         <v>0</v>
       </c>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>99</v>
+      </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -1866,7 +1937,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="11">
-        <v>515</v>
+        <v>614</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1909,8 +1980,12 @@
       <c r="M15" s="4">
         <v>40</v>
       </c>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="N15" s="4">
+        <v>94</v>
+      </c>
+      <c r="O15" s="4">
+        <v>3</v>
+      </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -1928,7 +2003,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="11">
-        <v>772</v>
+        <v>869</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -1971,8 +2046,12 @@
       <c r="M16" s="4">
         <v>0</v>
       </c>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="N16" s="4">
+        <v>107</v>
+      </c>
+      <c r="O16" s="4">
+        <v>104</v>
+      </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -1990,7 +2069,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="11">
-        <v>499</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2033,8 +2112,12 @@
       <c r="M17" s="4">
         <v>0</v>
       </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="N17" s="4">
+        <v>105</v>
+      </c>
+      <c r="O17" s="4">
+        <v>109</v>
+      </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -2052,7 +2135,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="11">
-        <v>597</v>
+        <v>811</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2095,8 +2178,12 @@
       <c r="M18" s="4">
         <v>30</v>
       </c>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>110</v>
+      </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -2114,7 +2201,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="11">
-        <v>853</v>
+        <v>963</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2157,8 +2244,12 @@
       <c r="M19" s="7">
         <v>88</v>
       </c>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
+      <c r="N19" s="7">
+        <v>1358</v>
+      </c>
+      <c r="O19" s="7">
+        <v>1518</v>
+      </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
@@ -2176,7 +2267,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="12">
-        <v>11013</v>
+        <v>13889</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2246,7 +2337,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFCFC00-2456-45AC-8738-5BCBDAA102B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20AFBB8-5C22-4CB2-99E6-03EEED98F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -566,18 +566,18 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C2" s="4">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="D2" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E2" s="5">
-        <v>3.78</v>
-      </c>
-      <c r="F2" s="15"/>
+        <v>3.55</v>
+      </c>
+      <c r="G2" s="15"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -585,18 +585,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="C3" s="4">
-        <v>588</v>
+        <v>767</v>
       </c>
       <c r="D3" s="11">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E3" s="5">
-        <v>2.89</v>
-      </c>
-      <c r="F3" s="15"/>
+        <v>2.82</v>
+      </c>
+      <c r="G3" s="15"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -604,18 +604,18 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C4" s="4">
-        <v>498</v>
+        <v>659</v>
       </c>
       <c r="D4" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4" s="5">
-        <v>2.78</v>
-      </c>
-      <c r="F4" s="15"/>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="G4" s="15"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -623,18 +623,18 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="C5" s="4">
-        <v>655</v>
+        <v>791</v>
       </c>
       <c r="D5" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5">
-        <v>3.33</v>
-      </c>
-      <c r="F5" s="15"/>
+        <v>3.27</v>
+      </c>
+      <c r="G5" s="15"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -642,18 +642,18 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="C6" s="4">
-        <v>699</v>
+        <v>870</v>
       </c>
       <c r="D6" s="11">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E6" s="5">
-        <v>2.89</v>
-      </c>
-      <c r="F6" s="15"/>
+        <v>2.91</v>
+      </c>
+      <c r="G6" s="15"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -661,18 +661,18 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="C7" s="4">
-        <v>667</v>
+        <v>839</v>
       </c>
       <c r="D7" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5">
-        <v>1.56</v>
-      </c>
-      <c r="F7" s="15"/>
+        <v>1.55</v>
+      </c>
+      <c r="G7" s="15"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -680,18 +680,18 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="C8" s="4">
-        <v>516</v>
+        <v>673</v>
       </c>
       <c r="D8" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5">
-        <v>2.89</v>
-      </c>
-      <c r="F8" s="15"/>
+        <v>2.64</v>
+      </c>
+      <c r="G8" s="15"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -699,18 +699,18 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="C9" s="4">
-        <v>598</v>
+        <v>756</v>
       </c>
       <c r="D9" s="11">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E9" s="5">
-        <v>3.56</v>
-      </c>
-      <c r="F9" s="15"/>
+        <v>3.73</v>
+      </c>
+      <c r="G9" s="15"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -718,18 +718,18 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="C10" s="4">
-        <v>706</v>
+        <v>857</v>
       </c>
       <c r="D10" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>2.11</v>
-      </c>
-      <c r="F10" s="15"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G10" s="15"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -737,18 +737,18 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C11" s="4">
-        <v>607</v>
+        <v>765</v>
       </c>
       <c r="D11" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5">
-        <v>2.67</v>
-      </c>
-      <c r="F11" s="15"/>
+        <v>2.73</v>
+      </c>
+      <c r="G11" s="15"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -756,18 +756,18 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="C12" s="4">
-        <v>557</v>
+        <v>727</v>
       </c>
       <c r="D12" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5">
-        <v>2.33</v>
-      </c>
-      <c r="F12" s="15"/>
+        <v>2.09</v>
+      </c>
+      <c r="G12" s="15"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -775,18 +775,18 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4">
-        <v>633</v>
+        <v>766</v>
       </c>
       <c r="D13" s="11">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E13" s="5">
-        <v>1.78</v>
-      </c>
-      <c r="F13" s="15"/>
+        <v>2.09</v>
+      </c>
+      <c r="G13" s="15"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -794,18 +794,18 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4">
-        <v>494</v>
+        <v>618</v>
       </c>
       <c r="D14" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E14" s="5">
-        <v>1.33</v>
-      </c>
-      <c r="F14" s="15"/>
+        <v>1.36</v>
+      </c>
+      <c r="G14" s="15"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -813,18 +813,18 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C15" s="4">
-        <v>581</v>
+        <v>691</v>
       </c>
       <c r="D15" s="11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5">
-        <v>3.22</v>
-      </c>
-      <c r="F15" s="15"/>
+        <v>2.91</v>
+      </c>
+      <c r="G15" s="15"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -832,18 +832,18 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C16" s="4">
-        <v>558</v>
+        <v>710</v>
       </c>
       <c r="D16" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E16" s="5">
-        <v>1.56</v>
-      </c>
-      <c r="F16" s="15"/>
+        <v>1.73</v>
+      </c>
+      <c r="G16" s="15"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,18 +851,18 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C17" s="4">
-        <v>688</v>
+        <v>868</v>
       </c>
       <c r="D17" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E17" s="5">
-        <v>1.67</v>
-      </c>
-      <c r="F17" s="15"/>
+        <v>1.73</v>
+      </c>
+      <c r="G17" s="15"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -870,18 +870,18 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4">
-        <v>730</v>
+        <v>824</v>
       </c>
       <c r="D18" s="11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E18" s="5">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="F18" s="15"/>
+        <v>2.27</v>
+      </c>
+      <c r="G18" s="15"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -889,18 +889,18 @@
         <v>23</v>
       </c>
       <c r="B19" s="7">
-        <v>3417</v>
+        <v>4052</v>
       </c>
       <c r="C19" s="7">
-        <v>10472</v>
+        <v>12924</v>
       </c>
       <c r="D19" s="12">
-        <v>383</v>
+        <v>466</v>
       </c>
       <c r="E19" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="F19" s="15"/>
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="G19" s="15"/>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1128,8 +1128,12 @@
       <c r="O2" s="4">
         <v>108</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>73</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
@@ -1145,7 +1149,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="11">
-        <v>964</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1194,8 +1198,12 @@
       <c r="O3" s="4">
         <v>100</v>
       </c>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="P3" s="4">
+        <v>112</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>104</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1211,7 +1219,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="11">
-        <v>806</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1260,8 +1268,12 @@
       <c r="O4" s="4">
         <v>106</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="P4" s="4">
+        <v>114</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>101</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -1277,7 +1289,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="11">
-        <v>684</v>
+        <v>899</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1326,8 +1338,12 @@
       <c r="O5" s="4">
         <v>126</v>
       </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+      <c r="P5" s="4">
+        <v>108</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>82</v>
+      </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -1343,7 +1359,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="11">
-        <v>891</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1392,8 +1408,12 @@
       <c r="O6" s="4">
         <v>111</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="P6" s="4">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>101</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -1409,7 +1429,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="11">
-        <v>967</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1458,8 +1478,12 @@
       <c r="O7" s="4">
         <v>105</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="P7" s="4">
+        <v>114</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>87</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -1475,7 +1499,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="11">
-        <v>863</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1524,8 +1548,12 @@
       <c r="O8" s="4">
         <v>110</v>
       </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="P8" s="4">
+        <v>106</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>96</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -1541,7 +1569,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="11">
-        <v>736</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1590,8 +1618,12 @@
       <c r="O9" s="4">
         <v>114</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="P9" s="4">
+        <v>110</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>106</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -1607,7 +1639,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="11">
-        <v>824</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1656,8 +1688,12 @@
       <c r="O10" s="4">
         <v>108</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="P10" s="4">
+        <v>105</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>96</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -1673,7 +1709,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="11">
-        <v>965</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1722,8 +1758,12 @@
       <c r="O11" s="4">
         <v>105</v>
       </c>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+      <c r="P11" s="4">
+        <v>85</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>100</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -1739,7 +1779,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="11">
-        <v>732</v>
+        <v>917</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1788,8 +1828,12 @@
       <c r="O12" s="4">
         <v>0</v>
       </c>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+      <c r="P12" s="4">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>116</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -1805,7 +1849,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="11">
-        <v>753</v>
+        <v>973</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1854,8 +1898,12 @@
       <c r="O13" s="4">
         <v>0</v>
       </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+      <c r="P13" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>51</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -1871,7 +1919,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="11">
-        <v>737</v>
+        <v>891</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1920,8 +1968,12 @@
       <c r="O14" s="4">
         <v>99</v>
       </c>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+      <c r="P14" s="4">
+        <v>101</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>53</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -1937,7 +1989,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="11">
-        <v>614</v>
+        <v>768</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1986,8 +2038,12 @@
       <c r="O15" s="4">
         <v>3</v>
       </c>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+      <c r="P15" s="4">
+        <v>121</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>27</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -2003,7 +2059,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="11">
-        <v>869</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2052,8 +2108,12 @@
       <c r="O16" s="4">
         <v>104</v>
       </c>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="P16" s="4">
+        <v>105</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>78</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -2069,7 +2129,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="11">
-        <v>710</v>
+        <v>893</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2118,8 +2178,12 @@
       <c r="O17" s="4">
         <v>109</v>
       </c>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="P17" s="4">
+        <v>106</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>100</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -2135,7 +2199,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="11">
-        <v>811</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2184,8 +2248,12 @@
       <c r="O18" s="4">
         <v>110</v>
       </c>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+      <c r="P18" s="4">
+        <v>117</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -2201,7 +2269,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="11">
-        <v>963</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2250,8 +2318,12 @@
       <c r="O19" s="7">
         <v>1518</v>
       </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="P19" s="7">
+        <v>1716</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>1371</v>
+      </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -2267,7 +2339,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="12">
-        <v>13889</v>
+        <v>16976</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2337,7 +2409,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>2.5</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20AFBB8-5C22-4CB2-99E6-03EEED98F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A06443-7497-4667-B6AC-3E8E93428511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -223,7 +223,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -566,18 +565,17 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="C2" s="4">
-        <v>743</v>
+        <v>878</v>
       </c>
       <c r="D2" s="11">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E2" s="5">
-        <v>3.55</v>
-      </c>
-      <c r="G2" s="15"/>
+        <v>3.62</v>
+      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -585,18 +583,17 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="C3" s="4">
-        <v>767</v>
+        <v>918</v>
       </c>
       <c r="D3" s="11">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5">
-        <v>2.82</v>
-      </c>
-      <c r="G3" s="15"/>
+        <v>2.77</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -604,18 +601,17 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="C4" s="4">
         <v>659</v>
       </c>
       <c r="D4" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" s="5">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="G4" s="15"/>
+        <v>2.46</v>
+      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -623,18 +619,17 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="C5" s="4">
-        <v>791</v>
+        <v>946</v>
       </c>
       <c r="D5" s="11">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E5" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="G5" s="15"/>
+        <v>3.38</v>
+      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -642,18 +637,17 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="C6" s="4">
-        <v>870</v>
+        <v>952</v>
       </c>
       <c r="D6" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6" s="5">
-        <v>2.91</v>
-      </c>
-      <c r="G6" s="15"/>
+        <v>2.69</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -661,18 +655,17 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C7" s="4">
-        <v>839</v>
+        <v>996</v>
       </c>
       <c r="D7" s="11">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5">
-        <v>1.55</v>
-      </c>
-      <c r="G7" s="15"/>
+        <v>1.92</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -680,18 +673,17 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="C8" s="4">
-        <v>673</v>
+        <v>814</v>
       </c>
       <c r="D8" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E8" s="5">
-        <v>2.64</v>
-      </c>
-      <c r="G8" s="15"/>
+        <v>2.69</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -699,18 +691,17 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="C9" s="4">
-        <v>756</v>
+        <v>902</v>
       </c>
       <c r="D9" s="11">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E9" s="5">
-        <v>3.73</v>
-      </c>
-      <c r="G9" s="15"/>
+        <v>3.69</v>
+      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -718,18 +709,17 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="C10" s="4">
-        <v>857</v>
+        <v>920</v>
       </c>
       <c r="D10" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E10" s="5">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="G10" s="15"/>
+        <v>2.46</v>
+      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -737,18 +727,17 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C11" s="4">
-        <v>765</v>
+        <v>907</v>
       </c>
       <c r="D11" s="11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E11" s="5">
-        <v>2.73</v>
-      </c>
-      <c r="G11" s="15"/>
+        <v>2.62</v>
+      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -756,18 +745,17 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="C12" s="4">
-        <v>727</v>
+        <v>867</v>
       </c>
       <c r="D12" s="11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E12" s="5">
-        <v>2.09</v>
-      </c>
-      <c r="G12" s="15"/>
+        <v>2.23</v>
+      </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -775,18 +763,17 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C13" s="4">
-        <v>766</v>
+        <v>929</v>
       </c>
       <c r="D13" s="11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E13" s="5">
-        <v>2.09</v>
-      </c>
-      <c r="G13" s="15"/>
+        <v>2.08</v>
+      </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -794,18 +781,17 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="C14" s="4">
-        <v>618</v>
+        <v>756</v>
       </c>
       <c r="D14" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E14" s="5">
-        <v>1.36</v>
-      </c>
-      <c r="G14" s="15"/>
+        <v>1.38</v>
+      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -813,18 +799,17 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>326</v>
+        <v>395</v>
       </c>
       <c r="C15" s="4">
-        <v>691</v>
+        <v>774</v>
       </c>
       <c r="D15" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" s="5">
-        <v>2.91</v>
-      </c>
-      <c r="G15" s="15"/>
+        <v>2.62</v>
+      </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -832,18 +817,17 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="C16" s="4">
-        <v>710</v>
+        <v>887</v>
       </c>
       <c r="D16" s="11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="G16" s="15"/>
+        <v>1.77</v>
+      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,18 +835,17 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C17" s="4">
-        <v>868</v>
+        <v>1024</v>
       </c>
       <c r="D17" s="11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E17" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="G17" s="15"/>
+        <v>2</v>
+      </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -870,18 +853,17 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="C18" s="4">
-        <v>824</v>
+        <v>949</v>
       </c>
       <c r="D18" s="11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E18" s="5">
-        <v>2.27</v>
-      </c>
-      <c r="G18" s="15"/>
+        <v>2.31</v>
+      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -889,18 +871,17 @@
         <v>23</v>
       </c>
       <c r="B19" s="7">
-        <v>4052</v>
+        <v>4773</v>
       </c>
       <c r="C19" s="7">
-        <v>12924</v>
+        <v>15078</v>
       </c>
       <c r="D19" s="12">
-        <v>466</v>
+        <v>555</v>
       </c>
       <c r="E19" s="8">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="G19" s="15"/>
+        <v>2.5099999999999998</v>
+      </c>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1134,10 +1115,18 @@
       <c r="Q2" s="4">
         <v>73</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="R2" s="4">
+        <v>102</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>31</v>
+      </c>
+      <c r="U2" s="4">
+        <v>78</v>
+      </c>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
@@ -1149,7 +1138,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="11">
-        <v>1037</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1204,10 +1193,18 @@
       <c r="Q3" s="4">
         <v>104</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="R3" s="4">
+        <v>104</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>91</v>
+      </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
@@ -1219,7 +1216,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="11">
-        <v>1022</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1274,10 +1271,18 @@
       <c r="Q4" s="4">
         <v>101</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>28</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
@@ -1289,7 +1294,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="11">
-        <v>899</v>
+        <v>927</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1344,10 +1349,18 @@
       <c r="Q5" s="4">
         <v>82</v>
       </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
+      <c r="R5" s="4">
+        <v>100</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>24</v>
+      </c>
+      <c r="U5" s="4">
+        <v>89</v>
+      </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
@@ -1359,7 +1372,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="11">
-        <v>1081</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1414,10 +1427,18 @@
       <c r="Q6" s="4">
         <v>101</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
+      <c r="R6" s="4">
+        <v>113</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
@@ -1429,7 +1450,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="11">
-        <v>1173</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1484,10 +1505,18 @@
       <c r="Q7" s="4">
         <v>87</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
+      <c r="R7" s="4">
+        <v>110</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>71</v>
+      </c>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
@@ -1499,7 +1528,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="11">
-        <v>1064</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1554,10 +1583,18 @@
       <c r="Q8" s="4">
         <v>96</v>
       </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
+      <c r="R8" s="4">
+        <v>102</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>89</v>
+      </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
@@ -1569,7 +1606,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="11">
-        <v>938</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1624,10 +1661,18 @@
       <c r="Q9" s="4">
         <v>106</v>
       </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="R9" s="4">
+        <v>106</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4">
+        <v>82</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
@@ -1639,7 +1684,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="11">
-        <v>1040</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1694,10 +1739,18 @@
       <c r="Q10" s="4">
         <v>96</v>
       </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4">
+        <v>16</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4">
+        <v>86</v>
+      </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
@@ -1709,7 +1762,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="11">
-        <v>1166</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1764,10 +1817,18 @@
       <c r="Q11" s="4">
         <v>100</v>
       </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
+      <c r="R11" s="4">
+        <v>99</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4">
+        <v>70</v>
+      </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
@@ -1779,7 +1840,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="11">
-        <v>917</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1834,10 +1895,18 @@
       <c r="Q12" s="4">
         <v>116</v>
       </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
+      <c r="R12" s="4">
+        <v>111</v>
+      </c>
+      <c r="S12" s="4">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4">
+        <v>86</v>
+      </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
@@ -1849,7 +1918,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="11">
-        <v>973</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1904,10 +1973,18 @@
       <c r="Q13" s="4">
         <v>51</v>
       </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
+      <c r="R13" s="4">
+        <v>107</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>81</v>
+      </c>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
@@ -1919,7 +1996,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="11">
-        <v>891</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1974,10 +2051,18 @@
       <c r="Q14" s="4">
         <v>53</v>
       </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+      <c r="R14" s="4">
+        <v>104</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>69</v>
+      </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
@@ -1989,7 +2074,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="11">
-        <v>768</v>
+        <v>941</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2044,10 +2129,18 @@
       <c r="Q15" s="4">
         <v>27</v>
       </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
+      <c r="R15" s="4">
+        <v>108</v>
+      </c>
+      <c r="S15" s="4">
+        <v>24</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>20</v>
+      </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -2059,7 +2152,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="11">
-        <v>1017</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2114,10 +2207,18 @@
       <c r="Q16" s="4">
         <v>78</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
+      <c r="R16" s="4">
+        <v>105</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>109</v>
+      </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
@@ -2129,7 +2230,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="11">
-        <v>893</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2184,10 +2285,18 @@
       <c r="Q17" s="4">
         <v>100</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
+      <c r="R17" s="4">
+        <v>98</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4">
+        <v>79</v>
+      </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
@@ -2199,7 +2308,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="11">
-        <v>1017</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2254,10 +2363,18 @@
       <c r="Q18" s="4">
         <v>0</v>
       </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
+      <c r="R18" s="4">
+        <v>53</v>
+      </c>
+      <c r="S18" s="4">
+        <v>27</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>103</v>
+      </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
@@ -2269,7 +2386,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="11">
-        <v>1080</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2324,10 +2441,18 @@
       <c r="Q19" s="7">
         <v>1371</v>
       </c>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
+      <c r="R19" s="7">
+        <v>1522</v>
+      </c>
+      <c r="S19" s="7">
+        <v>67</v>
+      </c>
+      <c r="T19" s="7">
+        <v>83</v>
+      </c>
+      <c r="U19" s="7">
+        <v>1203</v>
+      </c>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
@@ -2339,7 +2464,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="12">
-        <v>16976</v>
+        <v>19851</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2409,7 +2534,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>2.4900000000000002</v>
+        <v>2.5099999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A06443-7497-4667-B6AC-3E8E93428511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CE0EBB-C68B-4A19-9AC1-011BAE193ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -565,17 +565,18 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="C2" s="4">
-        <v>878</v>
+        <v>948</v>
       </c>
       <c r="D2" s="11">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5">
-        <v>3.62</v>
-      </c>
+        <v>3.57</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -583,17 +584,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C3" s="4">
-        <v>918</v>
+        <v>985</v>
       </c>
       <c r="D3" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5">
-        <v>2.77</v>
-      </c>
+        <v>2.71</v>
+      </c>
+      <c r="F3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -601,17 +603,18 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="C4" s="4">
-        <v>659</v>
+        <v>737</v>
       </c>
       <c r="D4" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" s="5">
-        <v>2.46</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -619,17 +622,18 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="C5" s="4">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D5" s="11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5" s="5">
-        <v>3.38</v>
-      </c>
+        <v>3.29</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -643,11 +647,12 @@
         <v>952</v>
       </c>
       <c r="D6" s="11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="5">
-        <v>2.69</v>
-      </c>
+        <v>2.57</v>
+      </c>
+      <c r="F6" s="1"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -655,17 +660,18 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C7" s="4">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="D7" s="11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5">
-        <v>1.92</v>
-      </c>
+        <v>1.93</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -673,17 +679,18 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="C8" s="4">
-        <v>814</v>
+        <v>893</v>
       </c>
       <c r="D8" s="11">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E8" s="5">
-        <v>2.69</v>
-      </c>
+        <v>2.79</v>
+      </c>
+      <c r="F8" s="1"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -691,17 +698,18 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="C9" s="4">
-        <v>902</v>
+        <v>981</v>
       </c>
       <c r="D9" s="11">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E9" s="5">
-        <v>3.69</v>
-      </c>
+        <v>3.64</v>
+      </c>
+      <c r="F9" s="1"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -709,17 +717,18 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="C10" s="4">
-        <v>920</v>
+        <v>996</v>
       </c>
       <c r="D10" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="5">
-        <v>2.46</v>
-      </c>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -727,17 +736,18 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C11" s="4">
-        <v>907</v>
+        <v>988</v>
       </c>
       <c r="D11" s="11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="5">
-        <v>2.62</v>
-      </c>
+        <v>2.71</v>
+      </c>
+      <c r="F11" s="1"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -745,17 +755,18 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="C12" s="4">
-        <v>867</v>
+        <v>948</v>
       </c>
       <c r="D12" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E12" s="5">
-        <v>2.23</v>
-      </c>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="F12" s="1"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -763,17 +774,18 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C13" s="4">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D13" s="11">
         <v>27</v>
       </c>
       <c r="E13" s="5">
-        <v>2.08</v>
-      </c>
+        <v>1.93</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -781,17 +793,18 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C14" s="4">
-        <v>756</v>
+        <v>810</v>
       </c>
       <c r="D14" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E14" s="5">
-        <v>1.38</v>
-      </c>
+        <v>1.43</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,7 +812,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C15" s="4">
         <v>774</v>
@@ -808,8 +821,9 @@
         <v>34</v>
       </c>
       <c r="E15" s="5">
-        <v>2.62</v>
-      </c>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="F15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -817,17 +831,18 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C16" s="4">
-        <v>887</v>
+        <v>967</v>
       </c>
       <c r="D16" s="11">
         <v>23</v>
       </c>
       <c r="E16" s="5">
-        <v>1.77</v>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="F16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -835,17 +850,18 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="C17" s="4">
-        <v>1024</v>
+        <v>1108</v>
       </c>
       <c r="D17" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" s="5">
-        <v>2</v>
-      </c>
+        <v>1.93</v>
+      </c>
+      <c r="F17" s="1"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -853,17 +869,18 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C18" s="4">
-        <v>949</v>
+        <v>1032</v>
       </c>
       <c r="D18" s="11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5">
-        <v>2.31</v>
-      </c>
+        <v>2.21</v>
+      </c>
+      <c r="F18" s="1"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -871,17 +888,18 @@
         <v>23</v>
       </c>
       <c r="B19" s="7">
-        <v>4773</v>
+        <v>5116</v>
       </c>
       <c r="C19" s="7">
-        <v>15078</v>
+        <v>16004</v>
       </c>
       <c r="D19" s="12">
-        <v>555</v>
+        <v>590</v>
       </c>
       <c r="E19" s="8">
-        <v>2.5099999999999998</v>
-      </c>
+        <v>2.48</v>
+      </c>
+      <c r="F19" s="1"/>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1127,7 +1145,9 @@
       <c r="U2" s="4">
         <v>78</v>
       </c>
-      <c r="V2" s="4"/>
+      <c r="V2" s="4">
+        <v>95</v>
+      </c>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
@@ -1138,7 +1158,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="11">
-        <v>1248</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1205,7 +1225,9 @@
       <c r="U3" s="4">
         <v>91</v>
       </c>
-      <c r="V3" s="4"/>
+      <c r="V3" s="4">
+        <v>95</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1216,7 +1238,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="11">
-        <v>1217</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1283,7 +1305,9 @@
       <c r="U4" s="4">
         <v>0</v>
       </c>
-      <c r="V4" s="4"/>
+      <c r="V4" s="4">
+        <v>104</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1294,7 +1318,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="11">
-        <v>927</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1361,7 +1385,9 @@
       <c r="U5" s="4">
         <v>89</v>
       </c>
-      <c r="V5" s="4"/>
+      <c r="V5" s="4">
+        <v>21</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1372,7 +1398,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="11">
-        <v>1294</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1439,7 +1465,9 @@
       <c r="U6" s="4">
         <v>0</v>
       </c>
-      <c r="V6" s="4"/>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -1517,7 +1545,9 @@
       <c r="U7" s="4">
         <v>71</v>
       </c>
-      <c r="V7" s="4"/>
+      <c r="V7" s="4">
+        <v>26</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1528,7 +1558,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="11">
-        <v>1245</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1595,7 +1625,9 @@
       <c r="U8" s="4">
         <v>89</v>
       </c>
-      <c r="V8" s="4"/>
+      <c r="V8" s="4">
+        <v>115</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1606,7 +1638,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="11">
-        <v>1129</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1673,7 +1705,9 @@
       <c r="U9" s="4">
         <v>82</v>
       </c>
-      <c r="V9" s="4"/>
+      <c r="V9" s="4">
+        <v>100</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1684,7 +1718,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="11">
-        <v>1228</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1751,7 +1785,9 @@
       <c r="U10" s="4">
         <v>86</v>
       </c>
-      <c r="V10" s="4"/>
+      <c r="V10" s="4">
+        <v>105</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1762,7 +1798,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="11">
-        <v>1268</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1829,7 +1865,9 @@
       <c r="U11" s="4">
         <v>70</v>
       </c>
-      <c r="V11" s="4"/>
+      <c r="V11" s="4">
+        <v>95</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1840,7 +1878,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="11">
-        <v>1086</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1907,7 +1945,9 @@
       <c r="U12" s="4">
         <v>86</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="4">
+        <v>109</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1918,7 +1958,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="11">
-        <v>1170</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1985,7 +2025,9 @@
       <c r="U13" s="4">
         <v>81</v>
       </c>
-      <c r="V13" s="4"/>
+      <c r="V13" s="4">
+        <v>15</v>
+      </c>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -1996,7 +2038,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="11">
-        <v>1079</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2063,7 +2105,9 @@
       <c r="U14" s="4">
         <v>69</v>
       </c>
-      <c r="V14" s="4"/>
+      <c r="V14" s="4">
+        <v>74</v>
+      </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -2074,7 +2118,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="11">
-        <v>941</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2141,7 +2185,9 @@
       <c r="U15" s="4">
         <v>20</v>
       </c>
-      <c r="V15" s="4"/>
+      <c r="V15" s="4">
+        <v>8</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2152,7 +2198,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="11">
-        <v>1169</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2219,7 +2265,9 @@
       <c r="U16" s="4">
         <v>109</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="4">
+        <v>103</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2230,7 +2278,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="11">
-        <v>1107</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2297,7 +2345,9 @@
       <c r="U17" s="4">
         <v>79</v>
       </c>
-      <c r="V17" s="4"/>
+      <c r="V17" s="4">
+        <v>102</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2308,7 +2358,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="11">
-        <v>1194</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2375,7 +2425,9 @@
       <c r="U18" s="4">
         <v>103</v>
       </c>
-      <c r="V18" s="4"/>
+      <c r="V18" s="4">
+        <v>102</v>
+      </c>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2386,7 +2438,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="11">
-        <v>1263</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2453,7 +2505,9 @@
       <c r="U19" s="7">
         <v>1203</v>
       </c>
-      <c r="V19" s="7"/>
+      <c r="V19" s="7">
+        <v>1269</v>
+      </c>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
@@ -2464,7 +2518,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="12">
-        <v>19851</v>
+        <v>21120</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2534,7 +2588,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>2.5099999999999998</v>
+        <v>2.48</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CE0EBB-C68B-4A19-9AC1-011BAE193ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D88398-9886-47CE-ADE0-F87A1604C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C2" s="4">
-        <v>948</v>
+        <v>1029</v>
       </c>
       <c r="D2" s="11">
         <v>50</v>
       </c>
       <c r="E2" s="5">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="C3" s="4">
-        <v>985</v>
+        <v>1106</v>
       </c>
       <c r="D3" s="11">
         <v>38</v>
       </c>
       <c r="E3" s="5">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,10 +603,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="C4" s="4">
-        <v>737</v>
+        <v>873</v>
       </c>
       <c r="D4" s="11">
         <v>35</v>
@@ -622,16 +622,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="C5" s="4">
-        <v>950</v>
+        <v>986</v>
       </c>
       <c r="D5" s="11">
         <v>46</v>
       </c>
       <c r="E5" s="5">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="C6" s="4">
-        <v>952</v>
+        <v>1078</v>
       </c>
       <c r="D6" s="11">
         <v>36</v>
       </c>
       <c r="E6" s="5">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="C7" s="4">
-        <v>1003</v>
+        <v>1143</v>
       </c>
       <c r="D7" s="11">
         <v>27</v>
       </c>
       <c r="E7" s="5">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="C8" s="4">
-        <v>893</v>
+        <v>1013</v>
       </c>
       <c r="D8" s="11">
         <v>39</v>
       </c>
       <c r="E8" s="5">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>347</v>
+        <v>402</v>
       </c>
       <c r="C9" s="4">
-        <v>981</v>
+        <v>1083</v>
       </c>
       <c r="D9" s="11">
         <v>51</v>
       </c>
       <c r="E9" s="5">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +717,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C10" s="4">
-        <v>996</v>
+        <v>1067</v>
       </c>
       <c r="D10" s="11">
         <v>34</v>
       </c>
       <c r="E10" s="5">
-        <v>2.4300000000000002</v>
+        <v>2.63</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="C11" s="4">
-        <v>988</v>
+        <v>1093</v>
       </c>
       <c r="D11" s="11">
         <v>38</v>
       </c>
       <c r="E11" s="5">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +755,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>331</v>
+        <v>385</v>
       </c>
       <c r="C12" s="4">
-        <v>948</v>
+        <v>1074</v>
       </c>
       <c r="D12" s="11">
         <v>34</v>
       </c>
       <c r="E12" s="5">
-        <v>2.4300000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C13" s="4">
-        <v>932</v>
+        <v>1069</v>
       </c>
       <c r="D13" s="11">
         <v>27</v>
       </c>
       <c r="E13" s="5">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4">
-        <v>810</v>
+        <v>872</v>
       </c>
       <c r="D14" s="11">
         <v>20</v>
       </c>
       <c r="E14" s="5">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>403</v>
+        <v>456</v>
       </c>
       <c r="C15" s="4">
-        <v>774</v>
+        <v>839</v>
       </c>
       <c r="D15" s="11">
         <v>34</v>
       </c>
       <c r="E15" s="5">
-        <v>2.4300000000000002</v>
+        <v>2.31</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C16" s="4">
-        <v>967</v>
+        <v>1010</v>
       </c>
       <c r="D16" s="11">
         <v>23</v>
       </c>
       <c r="E16" s="5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="C17" s="4">
-        <v>1108</v>
+        <v>1242</v>
       </c>
       <c r="D17" s="11">
         <v>27</v>
       </c>
       <c r="E17" s="5">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,16 +869,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="C18" s="4">
-        <v>1032</v>
+        <v>1132</v>
       </c>
       <c r="D18" s="11">
         <v>31</v>
       </c>
       <c r="E18" s="5">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="7">
-        <v>5116</v>
+        <v>5817</v>
       </c>
       <c r="C19" s="7">
-        <v>16004</v>
+        <v>17709</v>
       </c>
       <c r="D19" s="12">
         <v>590</v>
       </c>
       <c r="E19" s="8">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1148,8 +1148,12 @@
       <c r="V2" s="4">
         <v>95</v>
       </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="W2" s="4">
+        <v>101</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
@@ -1158,7 +1162,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="11">
-        <v>1343</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1228,8 +1232,12 @@
       <c r="V3" s="4">
         <v>95</v>
       </c>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
+      <c r="W3" s="4">
+        <v>95</v>
+      </c>
+      <c r="X3" s="4">
+        <v>67</v>
+      </c>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -1238,7 +1246,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="11">
-        <v>1312</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1308,8 +1316,12 @@
       <c r="V4" s="4">
         <v>104</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+      <c r="W4" s="4">
+        <v>102</v>
+      </c>
+      <c r="X4" s="4">
+        <v>79</v>
+      </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -1318,7 +1330,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="11">
-        <v>1031</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1388,8 +1400,12 @@
       <c r="V5" s="4">
         <v>21</v>
       </c>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
+      <c r="W5" s="4">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <v>61</v>
+      </c>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -1398,7 +1414,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="11">
-        <v>1315</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1468,8 +1484,12 @@
       <c r="V6" s="4">
         <v>0</v>
       </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+      <c r="W6" s="4">
+        <v>112</v>
+      </c>
+      <c r="X6" s="4">
+        <v>73</v>
+      </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1478,7 +1498,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="11">
-        <v>1286</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1548,8 +1568,12 @@
       <c r="V7" s="4">
         <v>26</v>
       </c>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="W7" s="4">
+        <v>101</v>
+      </c>
+      <c r="X7" s="4">
+        <v>74</v>
+      </c>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -1558,7 +1582,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="11">
-        <v>1271</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1628,8 +1652,12 @@
       <c r="V8" s="4">
         <v>115</v>
       </c>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
+      <c r="W8" s="4">
+        <v>105</v>
+      </c>
+      <c r="X8" s="4">
+        <v>74</v>
+      </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -1638,7 +1666,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="11">
-        <v>1244</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1708,8 +1736,12 @@
       <c r="V9" s="4">
         <v>100</v>
       </c>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="W9" s="4">
+        <v>98</v>
+      </c>
+      <c r="X9" s="4">
+        <v>59</v>
+      </c>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1718,7 +1750,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="11">
-        <v>1328</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1788,8 +1820,12 @@
       <c r="V10" s="4">
         <v>105</v>
       </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
+      <c r="W10" s="4">
+        <v>74</v>
+      </c>
+      <c r="X10" s="4">
+        <v>51</v>
+      </c>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
@@ -1798,7 +1834,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="11">
-        <v>1373</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1868,8 +1904,12 @@
       <c r="V11" s="4">
         <v>95</v>
       </c>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
+      <c r="W11" s="4">
+        <v>80</v>
+      </c>
+      <c r="X11" s="4">
+        <v>57</v>
+      </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1878,7 +1918,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="11">
-        <v>1181</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1948,8 +1988,12 @@
       <c r="V12" s="4">
         <v>109</v>
       </c>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
+      <c r="W12" s="4">
+        <v>108</v>
+      </c>
+      <c r="X12" s="4">
+        <v>72</v>
+      </c>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -1958,7 +2002,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="11">
-        <v>1279</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2028,8 +2072,12 @@
       <c r="V13" s="4">
         <v>15</v>
       </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
+      <c r="W13" s="4">
+        <v>100</v>
+      </c>
+      <c r="X13" s="4">
+        <v>64</v>
+      </c>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -2038,7 +2086,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="11">
-        <v>1094</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2108,8 +2156,12 @@
       <c r="V14" s="4">
         <v>74</v>
       </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="W14" s="4">
+        <v>66</v>
+      </c>
+      <c r="X14" s="4">
+        <v>44</v>
+      </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -2118,7 +2170,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="11">
-        <v>1015</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2188,8 +2240,12 @@
       <c r="V15" s="4">
         <v>8</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
+      <c r="W15" s="4">
+        <v>75</v>
+      </c>
+      <c r="X15" s="4">
+        <v>43</v>
+      </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -2198,7 +2254,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="11">
-        <v>1177</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2268,8 +2324,12 @@
       <c r="V16" s="4">
         <v>103</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>64</v>
+      </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -2278,7 +2338,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="11">
-        <v>1210</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2348,8 +2408,12 @@
       <c r="V17" s="4">
         <v>102</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+      <c r="W17" s="4">
+        <v>103</v>
+      </c>
+      <c r="X17" s="4">
+        <v>65</v>
+      </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2358,7 +2422,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="11">
-        <v>1296</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2428,8 +2492,12 @@
       <c r="V18" s="4">
         <v>102</v>
       </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
+      <c r="W18" s="4">
+        <v>102</v>
+      </c>
+      <c r="X18" s="4">
+        <v>37</v>
+      </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
@@ -2438,7 +2506,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="11">
-        <v>1365</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2508,8 +2576,12 @@
       <c r="V19" s="7">
         <v>1269</v>
       </c>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
+      <c r="W19" s="7">
+        <v>1422</v>
+      </c>
+      <c r="X19" s="7">
+        <v>984</v>
+      </c>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
@@ -2518,7 +2590,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="12">
-        <v>21120</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2588,7 +2660,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D88398-9886-47CE-ADE0-F87A1604C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712CAC05-0E6E-4433-BEAC-1EB139D24C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,18 +211,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="C2" s="4">
-        <v>1029</v>
-      </c>
-      <c r="D2" s="11">
-        <v>50</v>
-      </c>
-      <c r="E2" s="5">
-        <v>3.38</v>
+        <v>1109</v>
+      </c>
+      <c r="D2" s="9">
+        <v>59</v>
+      </c>
+      <c r="E2" s="13">
+        <v>3.47</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C3" s="4">
-        <v>1106</v>
-      </c>
-      <c r="D3" s="11">
-        <v>38</v>
-      </c>
-      <c r="E3" s="5">
-        <v>2.44</v>
+        <v>1186</v>
+      </c>
+      <c r="D3" s="9">
+        <v>42</v>
+      </c>
+      <c r="E3" s="13">
+        <v>2.4700000000000002</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C4" s="4">
-        <v>873</v>
-      </c>
-      <c r="D4" s="11">
-        <v>35</v>
-      </c>
-      <c r="E4" s="5">
-        <v>2.5</v>
+        <v>956</v>
+      </c>
+      <c r="D4" s="9">
+        <v>45</v>
+      </c>
+      <c r="E4" s="13">
+        <v>2.65</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,16 +622,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>390</v>
+        <v>435</v>
       </c>
       <c r="C5" s="4">
-        <v>986</v>
-      </c>
-      <c r="D5" s="11">
-        <v>46</v>
-      </c>
-      <c r="E5" s="5">
-        <v>3.13</v>
+        <v>1060</v>
+      </c>
+      <c r="D5" s="9">
+        <v>51</v>
+      </c>
+      <c r="E5" s="13">
+        <v>3</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="C6" s="4">
-        <v>1078</v>
-      </c>
-      <c r="D6" s="11">
-        <v>36</v>
-      </c>
-      <c r="E6" s="5">
-        <v>2.44</v>
+        <v>1088</v>
+      </c>
+      <c r="D6" s="9">
+        <v>42</v>
+      </c>
+      <c r="E6" s="13">
+        <v>2.4700000000000002</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C7" s="4">
         <v>1143</v>
       </c>
-      <c r="D7" s="11">
-        <v>27</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1.75</v>
+      <c r="D7" s="9">
+        <v>28</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1.65</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="C8" s="4">
-        <v>1013</v>
-      </c>
-      <c r="D8" s="11">
-        <v>39</v>
-      </c>
-      <c r="E8" s="5">
-        <v>2.69</v>
+        <v>1075</v>
+      </c>
+      <c r="D8" s="9">
+        <v>45</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2.65</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="C9" s="4">
-        <v>1083</v>
-      </c>
-      <c r="D9" s="11">
-        <v>51</v>
-      </c>
-      <c r="E9" s="5">
-        <v>3.75</v>
+        <v>1147</v>
+      </c>
+      <c r="D9" s="9">
+        <v>69</v>
+      </c>
+      <c r="E9" s="13">
+        <v>4.0599999999999996</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +717,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="C10" s="4">
         <v>1067</v>
       </c>
-      <c r="D10" s="11">
-        <v>34</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2.63</v>
+      <c r="D10" s="9">
+        <v>43</v>
+      </c>
+      <c r="E10" s="13">
+        <v>2.5299999999999998</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="C11" s="4">
-        <v>1093</v>
-      </c>
-      <c r="D11" s="11">
-        <v>38</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2.56</v>
+        <v>1168</v>
+      </c>
+      <c r="D11" s="9">
+        <v>45</v>
+      </c>
+      <c r="E11" s="13">
+        <v>2.65</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -760,11 +760,11 @@
       <c r="C12" s="4">
         <v>1074</v>
       </c>
-      <c r="D12" s="11">
-        <v>34</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2.25</v>
+      <c r="D12" s="9">
+        <v>36</v>
+      </c>
+      <c r="E12" s="13">
+        <v>2.12</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C13" s="4">
-        <v>1069</v>
-      </c>
-      <c r="D13" s="11">
-        <v>27</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1.88</v>
+        <v>1157</v>
+      </c>
+      <c r="D13" s="9">
+        <v>33</v>
+      </c>
+      <c r="E13" s="13">
+        <v>1.94</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C14" s="4">
-        <v>872</v>
-      </c>
-      <c r="D14" s="11">
-        <v>20</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1.56</v>
+        <v>935</v>
+      </c>
+      <c r="D14" s="9">
+        <v>25</v>
+      </c>
+      <c r="E14" s="13">
+        <v>1.47</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>456</v>
+        <v>518</v>
       </c>
       <c r="C15" s="4">
-        <v>839</v>
-      </c>
-      <c r="D15" s="11">
-        <v>34</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2.31</v>
+        <v>916</v>
+      </c>
+      <c r="D15" s="9">
+        <v>41</v>
+      </c>
+      <c r="E15" s="13">
+        <v>2.41</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C16" s="4">
-        <v>1010</v>
-      </c>
-      <c r="D16" s="11">
-        <v>23</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1.63</v>
+        <v>1088</v>
+      </c>
+      <c r="D16" s="9">
+        <v>28</v>
+      </c>
+      <c r="E16" s="13">
+        <v>1.65</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C17" s="4">
-        <v>1242</v>
-      </c>
-      <c r="D17" s="11">
-        <v>27</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2</v>
+        <v>1325</v>
+      </c>
+      <c r="D17" s="9">
+        <v>35</v>
+      </c>
+      <c r="E17" s="13">
+        <v>2.06</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,35 +869,35 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="C18" s="4">
-        <v>1132</v>
-      </c>
-      <c r="D18" s="11">
-        <v>31</v>
-      </c>
-      <c r="E18" s="5">
-        <v>2.13</v>
+        <v>1216</v>
+      </c>
+      <c r="D18" s="9">
+        <v>36</v>
+      </c>
+      <c r="E18" s="13">
+        <v>2.12</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="7">
-        <v>5817</v>
-      </c>
-      <c r="C19" s="7">
-        <v>17709</v>
-      </c>
-      <c r="D19" s="12">
-        <v>590</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.41</v>
+      <c r="B19" s="6">
+        <v>6358</v>
+      </c>
+      <c r="C19" s="6">
+        <v>18710</v>
+      </c>
+      <c r="D19" s="10">
+        <v>703</v>
+      </c>
+      <c r="E19" s="14">
+        <v>2.4300000000000002</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -984,100 +984,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12">
         <v>46113</v>
       </c>
-      <c r="C1" s="14">
+      <c r="C1" s="12">
         <v>46114</v>
       </c>
-      <c r="D1" s="14">
+      <c r="D1" s="12">
         <v>46115</v>
       </c>
-      <c r="E1" s="14">
+      <c r="E1" s="12">
         <v>46116</v>
       </c>
-      <c r="F1" s="14">
+      <c r="F1" s="12">
         <v>46117</v>
       </c>
-      <c r="G1" s="14">
+      <c r="G1" s="12">
         <v>46118</v>
       </c>
-      <c r="H1" s="14">
+      <c r="H1" s="12">
         <v>46119</v>
       </c>
-      <c r="I1" s="14">
+      <c r="I1" s="12">
         <v>46120</v>
       </c>
-      <c r="J1" s="14">
+      <c r="J1" s="12">
         <v>46121</v>
       </c>
-      <c r="K1" s="14">
+      <c r="K1" s="12">
         <v>46122</v>
       </c>
-      <c r="L1" s="14">
+      <c r="L1" s="12">
         <v>46123</v>
       </c>
-      <c r="M1" s="14">
+      <c r="M1" s="12">
         <v>46124</v>
       </c>
-      <c r="N1" s="14">
+      <c r="N1" s="12">
         <v>46125</v>
       </c>
-      <c r="O1" s="14">
+      <c r="O1" s="12">
         <v>46126</v>
       </c>
-      <c r="P1" s="14">
+      <c r="P1" s="12">
         <v>46127</v>
       </c>
-      <c r="Q1" s="14">
+      <c r="Q1" s="12">
         <v>46128</v>
       </c>
-      <c r="R1" s="14">
+      <c r="R1" s="12">
         <v>46129</v>
       </c>
-      <c r="S1" s="14">
+      <c r="S1" s="12">
         <v>46130</v>
       </c>
-      <c r="T1" s="14">
+      <c r="T1" s="12">
         <v>46131</v>
       </c>
-      <c r="U1" s="14">
+      <c r="U1" s="12">
         <v>46132</v>
       </c>
-      <c r="V1" s="14">
+      <c r="V1" s="12">
         <v>46133</v>
       </c>
-      <c r="W1" s="14">
+      <c r="W1" s="12">
         <v>46134</v>
       </c>
-      <c r="X1" s="14">
+      <c r="X1" s="12">
         <v>46135</v>
       </c>
-      <c r="Y1" s="14">
+      <c r="Y1" s="12">
         <v>46136</v>
       </c>
-      <c r="Z1" s="14">
+      <c r="Z1" s="12">
         <v>46137</v>
       </c>
-      <c r="AA1" s="14">
+      <c r="AA1" s="12">
         <v>46138</v>
       </c>
-      <c r="AB1" s="14">
+      <c r="AB1" s="12">
         <v>46139</v>
       </c>
-      <c r="AC1" s="14">
+      <c r="AC1" s="12">
         <v>46140</v>
       </c>
-      <c r="AD1" s="14">
+      <c r="AD1" s="12">
         <v>46141</v>
       </c>
-      <c r="AE1" s="14">
+      <c r="AE1" s="12">
         <v>46142</v>
       </c>
-      <c r="AF1" s="14" t="s">
+      <c r="AF1" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1154,15 +1154,21 @@
       <c r="X2" s="4">
         <v>0</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="Y2" s="4">
+        <v>105</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
-      <c r="AF2" s="11">
-        <v>1444</v>
+      <c r="AF2" s="9">
+        <v>1589</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1238,15 +1244,21 @@
       <c r="X3" s="4">
         <v>67</v>
       </c>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="Y3" s="4">
+        <v>102</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>0</v>
+      </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
-      <c r="AF3" s="11">
-        <v>1474</v>
+      <c r="AF3" s="9">
+        <v>1576</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1322,15 +1334,21 @@
       <c r="X4" s="4">
         <v>79</v>
       </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="Y4" s="4">
+        <v>107</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
-      <c r="AF4" s="11">
-        <v>1212</v>
+      <c r="AF4" s="9">
+        <v>1343</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1406,15 +1424,21 @@
       <c r="X5" s="4">
         <v>61</v>
       </c>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="Y5" s="4">
+        <v>96</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>23</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>0</v>
+      </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
-      <c r="AF5" s="11">
-        <v>1376</v>
+      <c r="AF5" s="9">
+        <v>1495</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1490,15 +1514,21 @@
       <c r="X6" s="4">
         <v>73</v>
       </c>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="Y6" s="4">
+        <v>38</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>12</v>
+      </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
-      <c r="AF6" s="11">
-        <v>1471</v>
+      <c r="AF6" s="9">
+        <v>1521</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1574,15 +1604,21 @@
       <c r="X7" s="4">
         <v>74</v>
       </c>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>3</v>
+      </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
-      <c r="AF7" s="11">
-        <v>1446</v>
+      <c r="AF7" s="9">
+        <v>1449</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1658,15 +1694,21 @@
       <c r="X8" s="4">
         <v>74</v>
       </c>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="Y8" s="4">
+        <v>104</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>0</v>
+      </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
-      <c r="AF8" s="11">
-        <v>1423</v>
+      <c r="AF8" s="9">
+        <v>1527</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1742,15 +1784,21 @@
       <c r="X9" s="4">
         <v>59</v>
       </c>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="Y9" s="4">
+        <v>108</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>0</v>
+      </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
-      <c r="AF9" s="11">
-        <v>1485</v>
+      <c r="AF9" s="9">
+        <v>1593</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1826,15 +1874,21 @@
       <c r="X10" s="4">
         <v>51</v>
       </c>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="Y10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>21</v>
+      </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
-      <c r="AF10" s="11">
-        <v>1498</v>
+      <c r="AF10" s="9">
+        <v>1520</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1910,15 +1964,21 @@
       <c r="X11" s="4">
         <v>57</v>
       </c>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="Y11" s="4">
+        <v>91</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>0</v>
+      </c>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
-      <c r="AF11" s="11">
-        <v>1318</v>
+      <c r="AF11" s="9">
+        <v>1409</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1994,14 +2054,20 @@
       <c r="X12" s="4">
         <v>72</v>
       </c>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>0</v>
+      </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
-      <c r="AF12" s="11">
+      <c r="AF12" s="9">
         <v>1459</v>
       </c>
     </row>
@@ -2078,15 +2144,21 @@
       <c r="X13" s="4">
         <v>64</v>
       </c>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="Y13" s="4">
+        <v>105</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
-      <c r="AF13" s="11">
-        <v>1258</v>
+      <c r="AF13" s="9">
+        <v>1363</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2162,15 +2234,21 @@
       <c r="X14" s="4">
         <v>44</v>
       </c>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="Y14" s="4">
+        <v>83</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>0</v>
+      </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
-      <c r="AF14" s="11">
-        <v>1125</v>
+      <c r="AF14" s="9">
+        <v>1208</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2246,15 +2324,21 @@
       <c r="X15" s="4">
         <v>43</v>
       </c>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="Y15" s="4">
+        <v>103</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>36</v>
+      </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
-      <c r="AF15" s="11">
-        <v>1295</v>
+      <c r="AF15" s="9">
+        <v>1434</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2330,15 +2414,21 @@
       <c r="X16" s="4">
         <v>64</v>
       </c>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="Y16" s="4">
+        <v>103</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>0</v>
+      </c>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
-      <c r="AF16" s="11">
-        <v>1274</v>
+      <c r="AF16" s="9">
+        <v>1377</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2414,15 +2504,21 @@
       <c r="X17" s="4">
         <v>65</v>
       </c>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="Y17" s="4">
+        <v>105</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>0</v>
+      </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
-      <c r="AF17" s="11">
-        <v>1464</v>
+      <c r="AF17" s="9">
+        <v>1569</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2498,145 +2594,157 @@
       <c r="X18" s="4">
         <v>37</v>
       </c>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="Y18" s="4">
+        <v>109</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>23</v>
+      </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
-      <c r="AF18" s="11">
-        <v>1504</v>
+      <c r="AF18" s="9">
+        <v>1636</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>1414</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>1329</v>
       </c>
-      <c r="D19" s="7">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7">
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
         <v>316</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>332</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>1507</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>1698</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <v>1558</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <v>1653</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>1009</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="6">
         <v>109</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="6">
         <v>88</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="6">
         <v>1358</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <v>1518</v>
       </c>
-      <c r="P19" s="7">
+      <c r="P19" s="6">
         <v>1716</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="6">
         <v>1371</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="6">
         <v>1522</v>
       </c>
-      <c r="S19" s="7">
+      <c r="S19" s="6">
         <v>67</v>
       </c>
-      <c r="T19" s="7">
+      <c r="T19" s="6">
         <v>83</v>
       </c>
-      <c r="U19" s="7">
+      <c r="U19" s="6">
         <v>1203</v>
       </c>
-      <c r="V19" s="7">
+      <c r="V19" s="6">
         <v>1269</v>
       </c>
-      <c r="W19" s="7">
+      <c r="W19" s="6">
         <v>1422</v>
       </c>
-      <c r="X19" s="7">
+      <c r="X19" s="6">
         <v>984</v>
       </c>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
-      <c r="AE19" s="7"/>
-      <c r="AF19" s="12">
-        <v>23526</v>
+      <c r="Y19" s="6">
+        <v>1359</v>
+      </c>
+      <c r="Z19" s="6">
+        <v>88</v>
+      </c>
+      <c r="AA19" s="6">
+        <v>95</v>
+      </c>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="10">
+        <v>25068</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
+      <c r="A20" s="8"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
+      <c r="A21" s="8"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
+      <c r="A22" s="8"/>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
+      <c r="A23" s="8"/>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+      <c r="A24" s="8"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+      <c r="A25" s="8"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+      <c r="A26" s="8"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+      <c r="A27" s="8"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+      <c r="A28" s="8"/>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+      <c r="A29" s="8"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+      <c r="A30" s="8"/>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+      <c r="A31" s="8"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+      <c r="A32" s="8"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="9"/>
+      <c r="C33" s="7"/>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="9"/>
+      <c r="C34" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:AD18">
@@ -2659,8 +2767,8 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>2.41</v>
+      <c r="A2" s="14">
+        <v>2.4300000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712CAC05-0E6E-4433-BEAC-1EB139D24C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3E34B3-BE8F-4284-9405-CA16E43637D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,8 +221,8 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="C2" s="4">
-        <v>1109</v>
+        <v>1244</v>
       </c>
       <c r="D2" s="9">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E2" s="13">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="C3" s="4">
-        <v>1186</v>
+        <v>1344</v>
       </c>
       <c r="D3" s="9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="13">
-        <v>2.4700000000000002</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="C4" s="4">
-        <v>956</v>
+        <v>1101</v>
       </c>
       <c r="D4" s="9">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" s="13">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,13 +622,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="C5" s="4">
-        <v>1060</v>
+        <v>1218</v>
       </c>
       <c r="D5" s="9">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E5" s="13">
         <v>3</v>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>433</v>
+        <v>499</v>
       </c>
       <c r="C6" s="4">
-        <v>1088</v>
+        <v>1225</v>
       </c>
       <c r="D6" s="9">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E6" s="13">
-        <v>2.4700000000000002</v>
+        <v>2.68</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>306</v>
+        <v>348</v>
       </c>
       <c r="C7" s="4">
-        <v>1143</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7" s="13">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>452</v>
+        <v>532</v>
       </c>
       <c r="C8" s="4">
-        <v>1075</v>
+        <v>1204</v>
       </c>
       <c r="D8" s="9">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8" s="13">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>446</v>
+        <v>515</v>
       </c>
       <c r="C9" s="4">
-        <v>1147</v>
+        <v>1283</v>
       </c>
       <c r="D9" s="9">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E9" s="13">
-        <v>4.0599999999999996</v>
+        <v>4.16</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +717,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="C10" s="4">
-        <v>1067</v>
+        <v>1145</v>
       </c>
       <c r="D10" s="9">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="13">
-        <v>2.5299999999999998</v>
+        <v>2.42</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="C11" s="4">
-        <v>1168</v>
+        <v>1315</v>
       </c>
       <c r="D11" s="9">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E11" s="13">
-        <v>2.65</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +755,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="C12" s="4">
-        <v>1074</v>
+        <v>1150</v>
       </c>
       <c r="D12" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="13">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="C13" s="4">
-        <v>1157</v>
+        <v>1325</v>
       </c>
       <c r="D13" s="9">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E13" s="13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="C14" s="4">
-        <v>935</v>
+        <v>982</v>
       </c>
       <c r="D14" s="9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="13">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>518</v>
+        <v>565</v>
       </c>
       <c r="C15" s="4">
-        <v>916</v>
+        <v>994</v>
       </c>
       <c r="D15" s="9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E15" s="13">
-        <v>2.41</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="C16" s="4">
-        <v>1088</v>
+        <v>1254</v>
       </c>
       <c r="D16" s="9">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E16" s="13">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C17" s="4">
-        <v>1325</v>
+        <v>1488</v>
       </c>
       <c r="D17" s="9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E17" s="13">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -875,10 +875,10 @@
         <v>1216</v>
       </c>
       <c r="D18" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E18" s="13">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>6358</v>
+        <v>7107</v>
       </c>
       <c r="C19" s="6">
-        <v>18710</v>
+        <v>20750</v>
       </c>
       <c r="D19" s="10">
-        <v>703</v>
+        <v>773</v>
       </c>
       <c r="E19" s="14">
-        <v>2.4300000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1163,12 +1163,16 @@
       <c r="AA2" s="4">
         <v>0</v>
       </c>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
+      <c r="AB2" s="4">
+        <v>87</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>95</v>
+      </c>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1589</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1253,12 +1257,16 @@
       <c r="AA3" s="4">
         <v>0</v>
       </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
+      <c r="AB3" s="4">
+        <v>105</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>103</v>
+      </c>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1576</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1343,12 +1351,16 @@
       <c r="AA4" s="4">
         <v>0</v>
       </c>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
+      <c r="AB4" s="4">
+        <v>109</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>107</v>
+      </c>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1343</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1433,12 +1445,16 @@
       <c r="AA5" s="4">
         <v>0</v>
       </c>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
+      <c r="AB5" s="4">
+        <v>95</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>104</v>
+      </c>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>1495</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1523,12 +1539,16 @@
       <c r="AA6" s="4">
         <v>12</v>
       </c>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
+      <c r="AB6" s="4">
+        <v>105</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>98</v>
+      </c>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1521</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1613,12 +1633,16 @@
       <c r="AA7" s="4">
         <v>3</v>
       </c>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
+      <c r="AB7" s="4">
+        <v>52</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>109</v>
+      </c>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1449</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1703,12 +1727,16 @@
       <c r="AA8" s="4">
         <v>0</v>
       </c>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
+      <c r="AB8" s="4">
+        <v>107</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>102</v>
+      </c>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1527</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1793,12 +1821,16 @@
       <c r="AA9" s="4">
         <v>0</v>
       </c>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
+      <c r="AB9" s="4">
+        <v>105</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>100</v>
+      </c>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1593</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1883,12 +1915,16 @@
       <c r="AA10" s="4">
         <v>21</v>
       </c>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>105</v>
+      </c>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1520</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1973,12 +2009,16 @@
       <c r="AA11" s="4">
         <v>0</v>
       </c>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
+      <c r="AB11" s="4">
+        <v>84</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>104</v>
+      </c>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1409</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2063,12 +2103,16 @@
       <c r="AA12" s="4">
         <v>0</v>
       </c>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
+      <c r="AB12" s="4">
+        <v>108</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>0</v>
+      </c>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1459</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2153,12 +2197,16 @@
       <c r="AA13" s="4">
         <v>0</v>
       </c>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
+      <c r="AB13" s="4">
+        <v>106</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>101</v>
+      </c>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1363</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2243,12 +2291,16 @@
       <c r="AA14" s="4">
         <v>0</v>
       </c>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
+      <c r="AB14" s="4">
+        <v>68</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>14</v>
+      </c>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1208</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2333,12 +2385,16 @@
       <c r="AA15" s="4">
         <v>36</v>
       </c>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
+      <c r="AB15" s="4">
+        <v>102</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>23</v>
+      </c>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1434</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2423,12 +2479,16 @@
       <c r="AA16" s="4">
         <v>0</v>
       </c>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
+      <c r="AB16" s="4">
+        <v>101</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>102</v>
+      </c>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1377</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2513,12 +2573,16 @@
       <c r="AA17" s="4">
         <v>0</v>
       </c>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
+      <c r="AB17" s="4">
+        <v>85</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>103</v>
+      </c>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1569</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2603,8 +2667,12 @@
       <c r="AA18" s="4">
         <v>23</v>
       </c>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
+      <c r="AB18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>0</v>
+      </c>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
@@ -2693,12 +2761,16 @@
       <c r="AA19" s="6">
         <v>95</v>
       </c>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
+      <c r="AB19" s="6">
+        <v>1419</v>
+      </c>
+      <c r="AC19" s="6">
+        <v>1370</v>
+      </c>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="10">
-        <v>25068</v>
+        <v>27857</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2768,7 +2840,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.4300000000000002</v>
+        <v>2.39</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3E34B3-BE8F-4284-9405-CA16E43637D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B85BC90-09C0-40B2-8A3F-2AA3A7B1FAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -221,8 +221,8 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -571,10 +571,10 @@
         <v>1244</v>
       </c>
       <c r="D2" s="9">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E2" s="13">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="C3" s="4">
-        <v>1344</v>
+        <v>1439</v>
       </c>
       <c r="D3" s="9">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E3" s="13">
-        <v>2.2599999999999998</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="C4" s="4">
-        <v>1101</v>
+        <v>1183</v>
       </c>
       <c r="D4" s="9">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E4" s="13">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,16 +622,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="C5" s="4">
-        <v>1218</v>
+        <v>1285</v>
       </c>
       <c r="D5" s="9">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E5" s="13">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>499</v>
+        <v>555</v>
       </c>
       <c r="C6" s="4">
-        <v>1225</v>
+        <v>1366</v>
       </c>
       <c r="D6" s="9">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E6" s="13">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="C7" s="4">
-        <v>1262</v>
+        <v>1419</v>
       </c>
       <c r="D7" s="9">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E7" s="13">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="C8" s="4">
-        <v>1204</v>
+        <v>1244</v>
       </c>
       <c r="D8" s="9">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E8" s="13">
-        <v>2.68</v>
+        <v>3.58</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>515</v>
+        <v>580</v>
       </c>
       <c r="C9" s="4">
-        <v>1283</v>
+        <v>1427</v>
       </c>
       <c r="D9" s="9">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E9" s="13">
-        <v>4.16</v>
+        <v>4.95</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +717,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>480</v>
+        <v>541</v>
       </c>
       <c r="C10" s="4">
-        <v>1145</v>
+        <v>1289</v>
       </c>
       <c r="D10" s="9">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E10" s="13">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4">
-        <v>1315</v>
+        <v>1465</v>
       </c>
       <c r="D11" s="9">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E11" s="13">
-        <v>2.5299999999999998</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +755,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="C12" s="4">
-        <v>1150</v>
+        <v>1321</v>
       </c>
       <c r="D12" s="9">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E12" s="13">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="C13" s="4">
-        <v>1325</v>
+        <v>1482</v>
       </c>
       <c r="D13" s="9">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E13" s="13">
-        <v>1.95</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -799,10 +799,10 @@
         <v>982</v>
       </c>
       <c r="D14" s="9">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E14" s="13">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="C15" s="4">
-        <v>994</v>
+        <v>1068</v>
       </c>
       <c r="D15" s="9">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E15" s="13">
-        <v>2.2599999999999998</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="C16" s="4">
-        <v>1254</v>
+        <v>1366</v>
       </c>
       <c r="D16" s="9">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" s="13">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="C17" s="4">
-        <v>1488</v>
+        <v>1666</v>
       </c>
       <c r="D17" s="9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" s="13">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,16 +869,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="C18" s="4">
-        <v>1216</v>
+        <v>1375</v>
       </c>
       <c r="D18" s="9">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E18" s="13">
-        <v>2</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>7107</v>
+        <v>7744</v>
       </c>
       <c r="C19" s="6">
-        <v>20750</v>
+        <v>22621</v>
       </c>
       <c r="D19" s="10">
-        <v>773</v>
+        <v>900</v>
       </c>
       <c r="E19" s="14">
-        <v>2.39</v>
+        <v>2.79</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1169,8 +1169,12 @@
       <c r="AC2" s="4">
         <v>95</v>
       </c>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
       <c r="AF2" s="9">
         <v>1771</v>
       </c>
@@ -1263,10 +1267,14 @@
       <c r="AC3" s="4">
         <v>103</v>
       </c>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
+      <c r="AD3" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>27</v>
+      </c>
       <c r="AF3" s="9">
-        <v>1784</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1357,10 +1365,14 @@
       <c r="AC4" s="4">
         <v>107</v>
       </c>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
+      <c r="AD4" s="4">
+        <v>102</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
       <c r="AF4" s="9">
-        <v>1559</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1451,10 +1463,14 @@
       <c r="AC5" s="4">
         <v>104</v>
       </c>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
+      <c r="AD5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>101</v>
+      </c>
       <c r="AF5" s="9">
-        <v>1694</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1545,10 +1561,14 @@
       <c r="AC6" s="4">
         <v>98</v>
       </c>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
+      <c r="AD6" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>93</v>
+      </c>
       <c r="AF6" s="9">
-        <v>1724</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1639,10 +1659,14 @@
       <c r="AC7" s="4">
         <v>109</v>
       </c>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
+      <c r="AD7" s="4">
+        <v>111</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>86</v>
+      </c>
       <c r="AF7" s="9">
-        <v>1610</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1733,10 +1757,14 @@
       <c r="AC8" s="4">
         <v>102</v>
       </c>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>59</v>
+      </c>
       <c r="AF8" s="9">
-        <v>1736</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1827,10 +1855,14 @@
       <c r="AC9" s="4">
         <v>100</v>
       </c>
-      <c r="AD9" s="4"/>
-      <c r="AE9" s="4"/>
+      <c r="AD9" s="4">
+        <v>99</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>110</v>
+      </c>
       <c r="AF9" s="9">
-        <v>1798</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1921,10 +1953,14 @@
       <c r="AC10" s="4">
         <v>105</v>
       </c>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
+      <c r="AD10" s="4">
+        <v>105</v>
+      </c>
+      <c r="AE10" s="4">
+        <v>100</v>
+      </c>
       <c r="AF10" s="9">
-        <v>1625</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -2015,10 +2051,14 @@
       <c r="AC11" s="4">
         <v>104</v>
       </c>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
+      <c r="AD11" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>80</v>
+      </c>
       <c r="AF11" s="9">
-        <v>1597</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2109,10 +2149,14 @@
       <c r="AC12" s="4">
         <v>0</v>
       </c>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
+      <c r="AD12" s="4">
+        <v>112</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>110</v>
+      </c>
       <c r="AF12" s="9">
-        <v>1567</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2203,10 +2247,14 @@
       <c r="AC13" s="4">
         <v>101</v>
       </c>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
+      <c r="AD13" s="4">
+        <v>114</v>
+      </c>
+      <c r="AE13" s="4">
+        <v>81</v>
+      </c>
       <c r="AF13" s="9">
-        <v>1570</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2297,8 +2345,12 @@
       <c r="AC14" s="4">
         <v>14</v>
       </c>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
+      <c r="AD14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="4">
+        <v>0</v>
+      </c>
       <c r="AF14" s="9">
         <v>1290</v>
       </c>
@@ -2391,10 +2443,14 @@
       <c r="AC15" s="4">
         <v>23</v>
       </c>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
+      <c r="AD15" s="4">
+        <v>64</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>51</v>
+      </c>
       <c r="AF15" s="9">
-        <v>1559</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2485,10 +2541,14 @@
       <c r="AC16" s="4">
         <v>102</v>
       </c>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
+      <c r="AD16" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>67</v>
+      </c>
       <c r="AF16" s="9">
-        <v>1580</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2579,10 +2639,14 @@
       <c r="AC17" s="4">
         <v>103</v>
       </c>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
+      <c r="AD17" s="4">
+        <v>106</v>
+      </c>
+      <c r="AE17" s="4">
+        <v>107</v>
+      </c>
       <c r="AF17" s="9">
-        <v>1757</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2673,10 +2737,14 @@
       <c r="AC18" s="4">
         <v>0</v>
       </c>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
+      <c r="AD18" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE18" s="4">
+        <v>103</v>
+      </c>
       <c r="AF18" s="9">
-        <v>1636</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2767,10 +2835,14 @@
       <c r="AC19" s="6">
         <v>1370</v>
       </c>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
+      <c r="AD19" s="6">
+        <v>1333</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>1175</v>
+      </c>
       <c r="AF19" s="10">
-        <v>27857</v>
+        <v>30365</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2840,7 +2912,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.39</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B85BC90-09C0-40B2-8A3F-2AA3A7B1FAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E826D9-AB1E-4DEE-9F1B-F70D4E89E69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -221,8 +221,9 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -573,10 +574,13 @@
       <c r="D2" s="9">
         <v>69</v>
       </c>
-      <c r="E2" s="13">
-        <v>3.63</v>
+      <c r="E2" s="14">
+        <v>3.45</v>
       </c>
       <c r="F2" s="1"/>
+      <c r="G2">
+        <v>3.45</v>
+      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -592,10 +596,13 @@
       <c r="D3" s="9">
         <v>48</v>
       </c>
-      <c r="E3" s="13">
-        <v>2.5299999999999998</v>
+      <c r="E3" s="14">
+        <v>2.4</v>
       </c>
       <c r="F3" s="1"/>
+      <c r="G3">
+        <v>2.4</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -611,10 +618,13 @@
       <c r="D4" s="9">
         <v>53</v>
       </c>
-      <c r="E4" s="13">
-        <v>2.79</v>
+      <c r="E4" s="14">
+        <v>2.65</v>
       </c>
       <c r="F4" s="1"/>
+      <c r="G4">
+        <v>2.65</v>
+      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -630,10 +640,13 @@
       <c r="D5" s="9">
         <v>63</v>
       </c>
-      <c r="E5" s="13">
-        <v>3.32</v>
+      <c r="E5" s="14">
+        <v>3.15</v>
       </c>
       <c r="F5" s="1"/>
+      <c r="G5">
+        <v>3.15</v>
+      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -649,10 +662,13 @@
       <c r="D6" s="9">
         <v>57</v>
       </c>
-      <c r="E6" s="13">
-        <v>3</v>
+      <c r="E6" s="14">
+        <v>2.85</v>
       </c>
       <c r="F6" s="1"/>
+      <c r="G6">
+        <v>2.85</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -668,10 +684,13 @@
       <c r="D7" s="9">
         <v>38</v>
       </c>
-      <c r="E7" s="13">
-        <v>2</v>
+      <c r="E7" s="14">
+        <v>1.9</v>
       </c>
       <c r="F7" s="1"/>
+      <c r="G7">
+        <v>1.9</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -687,10 +706,13 @@
       <c r="D8" s="9">
         <v>68</v>
       </c>
-      <c r="E8" s="13">
-        <v>3.58</v>
+      <c r="E8" s="14">
+        <v>3.4</v>
       </c>
       <c r="F8" s="1"/>
+      <c r="G8">
+        <v>3.4</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -706,10 +728,13 @@
       <c r="D9" s="9">
         <v>94</v>
       </c>
-      <c r="E9" s="13">
-        <v>4.95</v>
+      <c r="E9" s="14">
+        <v>4.7</v>
       </c>
       <c r="F9" s="1"/>
+      <c r="G9">
+        <v>4.7</v>
+      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -725,10 +750,13 @@
       <c r="D10" s="9">
         <v>59</v>
       </c>
-      <c r="E10" s="13">
-        <v>3.11</v>
+      <c r="E10" s="14">
+        <v>2.95</v>
       </c>
       <c r="F10" s="1"/>
+      <c r="G10">
+        <v>2.95</v>
+      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -744,10 +772,13 @@
       <c r="D11" s="9">
         <v>57</v>
       </c>
-      <c r="E11" s="13">
-        <v>3</v>
+      <c r="E11" s="14">
+        <v>2.85</v>
       </c>
       <c r="F11" s="1"/>
+      <c r="G11">
+        <v>2.85</v>
+      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -763,10 +794,13 @@
       <c r="D12" s="9">
         <v>45</v>
       </c>
-      <c r="E12" s="13">
-        <v>2.37</v>
+      <c r="E12" s="14">
+        <v>2.25</v>
       </c>
       <c r="F12" s="1"/>
+      <c r="G12">
+        <v>2.25</v>
+      </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -782,10 +816,13 @@
       <c r="D13" s="9">
         <v>43</v>
       </c>
-      <c r="E13" s="13">
-        <v>2.2599999999999998</v>
+      <c r="E13" s="14">
+        <v>2.15</v>
       </c>
       <c r="F13" s="1"/>
+      <c r="G13">
+        <v>2.15</v>
+      </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -801,10 +838,13 @@
       <c r="D14" s="9">
         <v>32</v>
       </c>
-      <c r="E14" s="13">
-        <v>1.68</v>
+      <c r="E14" s="14">
+        <v>1.6</v>
       </c>
       <c r="F14" s="1"/>
+      <c r="G14">
+        <v>1.6</v>
+      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -820,10 +860,13 @@
       <c r="D15" s="9">
         <v>47</v>
       </c>
-      <c r="E15" s="13">
-        <v>2.4700000000000002</v>
+      <c r="E15" s="14">
+        <v>2.35</v>
       </c>
       <c r="F15" s="1"/>
+      <c r="G15">
+        <v>2.35</v>
+      </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -839,10 +882,13 @@
       <c r="D16" s="9">
         <v>38</v>
       </c>
-      <c r="E16" s="13">
-        <v>2</v>
+      <c r="E16" s="14">
+        <v>1.9</v>
       </c>
       <c r="F16" s="1"/>
+      <c r="G16">
+        <v>1.9</v>
+      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -858,10 +904,13 @@
       <c r="D17" s="9">
         <v>42</v>
       </c>
-      <c r="E17" s="13">
-        <v>2.21</v>
+      <c r="E17" s="14">
+        <v>2.1</v>
       </c>
       <c r="F17" s="1"/>
+      <c r="G17">
+        <v>2.1</v>
+      </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,10 +926,13 @@
       <c r="D18" s="9">
         <v>47</v>
       </c>
-      <c r="E18" s="13">
-        <v>2.4700000000000002</v>
+      <c r="E18" s="14">
+        <v>2.35</v>
       </c>
       <c r="F18" s="1"/>
+      <c r="G18">
+        <v>2.35</v>
+      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -896,10 +948,13 @@
       <c r="D19" s="10">
         <v>900</v>
       </c>
-      <c r="E19" s="14">
-        <v>2.79</v>
+      <c r="E19" s="15">
+        <v>2.65</v>
       </c>
       <c r="F19" s="1"/>
+      <c r="G19">
+        <v>2.6470588235294117</v>
+      </c>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2911,8 +2966,8 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>2.79</v>
+      <c r="A2" s="13">
+        <v>2.65</v>
       </c>
     </row>
   </sheetData>

--- a/April-2026.xlsx
+++ b/April-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E826D9-AB1E-4DEE-9F1B-F70D4E89E69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5872516A-A14E-4FC2-AD5C-288AB4BB5B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -221,7 +221,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -574,7 +573,7 @@
       <c r="D2" s="9">
         <v>69</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>3.45</v>
       </c>
       <c r="F2" s="1"/>
@@ -596,7 +595,7 @@
       <c r="D3" s="9">
         <v>48</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>2.4</v>
       </c>
       <c r="F3" s="1"/>
@@ -616,14 +615,14 @@
         <v>1183</v>
       </c>
       <c r="D4" s="9">
-        <v>53</v>
-      </c>
-      <c r="E4" s="14">
-        <v>2.65</v>
+        <v>52</v>
+      </c>
+      <c r="E4" s="13">
+        <v>2.6</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -640,7 +639,7 @@
       <c r="D5" s="9">
         <v>63</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>3.15</v>
       </c>
       <c r="F5" s="1"/>
@@ -662,7 +661,7 @@
       <c r="D6" s="9">
         <v>57</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>2.85</v>
       </c>
       <c r="F6" s="1"/>
@@ -684,7 +683,7 @@
       <c r="D7" s="9">
         <v>38</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>1.9</v>
       </c>
       <c r="F7" s="1"/>
@@ -706,7 +705,7 @@
       <c r="D8" s="9">
         <v>68</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>3.4</v>
       </c>
       <c r="F8" s="1"/>
@@ -726,14 +725,14 @@
         <v>1427</v>
       </c>
       <c r="D9" s="9">
-        <v>94</v>
-      </c>
-      <c r="E9" s="14">
-        <v>4.7</v>
+        <v>93</v>
+      </c>
+      <c r="E9" s="13">
+        <v>4.6500000000000004</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9">
-        <v>4.7</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="H9" s="1"/>
     </row>
@@ -750,7 +749,7 @@
       <c r="D10" s="9">
         <v>59</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>2.95</v>
       </c>
       <c r="F10" s="1"/>
@@ -772,7 +771,7 @@
       <c r="D11" s="9">
         <v>57</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>2.85</v>
       </c>
       <c r="F11" s="1"/>
@@ -794,7 +793,7 @@
       <c r="D12" s="9">
         <v>45</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>2.25</v>
       </c>
       <c r="F12" s="1"/>
@@ -816,7 +815,7 @@
       <c r="D13" s="9">
         <v>43</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <v>2.15</v>
       </c>
       <c r="F13" s="1"/>
@@ -838,7 +837,7 @@
       <c r="D14" s="9">
         <v>32</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>1.6</v>
       </c>
       <c r="F14" s="1"/>
@@ -860,7 +859,7 @@
       <c r="D15" s="9">
         <v>47</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>2.35</v>
       </c>
       <c r="F15" s="1"/>
@@ -882,7 +881,7 @@
       <c r="D16" s="9">
         <v>38</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="13">
         <v>1.9</v>
       </c>
       <c r="F16" s="1"/>
@@ -904,7 +903,7 @@
       <c r="D17" s="9">
         <v>42</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="13">
         <v>2.1</v>
       </c>
       <c r="F17" s="1"/>
@@ -926,7 +925,7 @@
       <c r="D18" s="9">
         <v>47</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="13">
         <v>2.35</v>
       </c>
       <c r="F18" s="1"/>
@@ -946,14 +945,14 @@
         <v>22621</v>
       </c>
       <c r="D19" s="10">
-        <v>900</v>
-      </c>
-      <c r="E19" s="15">
-        <v>2.65</v>
+        <v>898</v>
+      </c>
+      <c r="E19" s="14">
+        <v>2.6411764705882352</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19">
-        <v>2.6470588235294117</v>
+        <v>2.6411764705882352</v>
       </c>
       <c r="H19" s="1"/>
     </row>
@@ -2966,8 +2965,8 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
-        <v>2.65</v>
+      <c r="A2" s="14">
+        <v>2.6411764705882352</v>
       </c>
     </row>
   </sheetData>
